--- a/data/trans_orig/IP16B03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16B03-Habitat-trans_orig.xlsx
@@ -1488,7 +1488,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13689</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,94%</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9105</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>2909</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>63,64%</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
